--- a/SBM-corps-FHIR/ig/observations-summary.xlsx
+++ b/SBM-corps-FHIR/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="105">
   <si>
     <t>Profile</t>
   </si>
@@ -50,13 +50,13 @@
     <t>fr-accidents-transfusionnels</t>
   </si>
   <si>
-    <t>Observation - Fr Observation Accidents Transfusionnels</t>
+    <t>Observation - Fr Accidents transfusionnels</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-146</t>
+    <t>terminologie-cisis#MED-146</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
@@ -71,76 +71,91 @@
     <t>fr-administration-de-derives-du-sang</t>
   </si>
   <si>
-    <t>Observation - Fr Observation Administration de derivés du sang</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-147</t>
+    <t>Observation - Fr Administration de derivés du sang</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#MED-147</t>
+  </si>
+  <si>
+    <t>booleanĵ</t>
+  </si>
+  <si>
+    <t>fr-batterie-examen-et-surveillance-prenataux</t>
+  </si>
+  <si>
+    <t>Observation - Fr Batterie examens et surveillance prénataux</t>
+  </si>
+  <si>
+    <t>LOINC#XX-ANTENATALTESTINGBATTERY</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
   </si>
   <si>
-    <t>booleanĵ</t>
-  </si>
-  <si>
-    <t>fr-batterie-examen-et-surveillance-prenataux</t>
-  </si>
-  <si>
-    <t>Observation - Fr Observation Batterie Examens Et Surveillance Prenataux</t>
-  </si>
-  <si>
-    <t>LOINC#XX-ANTENATALTESTINGBATTERY</t>
-  </si>
-  <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
   <si>
     <t>fr-en-rapport-avec-accident-travail</t>
   </si>
   <si>
-    <t>Observation - Fr Observation En rapport avec accident travail</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-180</t>
+    <t>Observation - Fr En rapport avec accident travail</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-180</t>
   </si>
   <si>
     <t>fr-en-rapport-avec-ald</t>
   </si>
   <si>
-    <t>Observation - Fr Observation En rapport avec ALD</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-574</t>
+    <t>Observation - Fr En rapport avec ALD</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#MED-574</t>
   </si>
   <si>
     <t>fr-en-rapport-avec-la-prevention</t>
   </si>
   <si>
-    <t>Observation - Fr Observation En rapport avec la prévention</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-295</t>
+    <t>Observation - Fr En rapport avec la prévention</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-295</t>
+  </si>
+  <si>
+    <t>fr-historique-de-la-grossesse</t>
+  </si>
+  <si>
+    <t>Observation - Fr Historique de la grossesse</t>
+  </si>
+  <si>
+    <t>null#118185001</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
   </si>
   <si>
     <t>fr-hors-nomenclature</t>
   </si>
   <si>
-    <t>Observation - Fr Observation Hors nomenclature</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-298</t>
+    <t>Observation - Fr Hors nomenclature</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-298</t>
   </si>
   <si>
     <t>fr-non-remboursable</t>
   </si>
   <si>
-    <t>Observation - Fr Observation Non Remboursable</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-181</t>
-  </si>
-  <si>
-    <t>Fr-objectifs-de-reference-DICOM</t>
+    <t>Observation - Fr Non remboursable</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-181</t>
+  </si>
+  <si>
+    <t>fr-objectifs-de-reference-dicom</t>
   </si>
   <si>
     <t>Observation - Fr Objectifs De Reference DICOM</t>
@@ -149,46 +164,46 @@
     <t>ActCode#ASSERTION</t>
   </si>
   <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>fr-observation-contexte</t>
+  </si>
+  <si>
+    <t>Observation - Fr Contexte de l'acte</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-299</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-difficulte</t>
+  </si>
+  <si>
+    <t>Observation - Fr Difficulté de l'acte</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#GEN-023</t>
+  </si>
+  <si>
+    <t>fr-observation-evaluation</t>
+  </si>
+  <si>
+    <t>Observation - Fr Évaluation</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>fr-observation-contexte</t>
-  </si>
-  <si>
-    <t>Observation - Fr Contexte de l'acte</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-299</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-difficulte</t>
-  </si>
-  <si>
-    <t>Observation - Fr Difficulté de l'acte</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-023</t>
-  </si>
-  <si>
-    <t>fr-observation-evaluation</t>
-  </si>
-  <si>
-    <t>Observation - Évaluation</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#survey</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
     <t>fr-observation-habitus-mode-de-vie</t>
   </si>
   <si>
-    <t>FR - Habitus / Mode de vie</t>
+    <t>Observation - Fr Habitus / Mode de vie</t>
   </si>
   <si>
     <t>Observation Category Codes#social-history</t>
@@ -200,7 +215,7 @@
     <t>fr-observation-modalite-entree</t>
   </si>
   <si>
-    <t>FR - Modalité d'entrée</t>
+    <t>Observation - Fr Modalité d'entrée</t>
   </si>
   <si>
     <t>[not stated]#ORG-070</t>
@@ -209,19 +224,109 @@
     <t>fr-observation-modalite-sortie</t>
   </si>
   <si>
-    <t>FR - Modalité de sortie</t>
+    <t>Observation - Fr Modalité de sortie</t>
   </si>
   <si>
     <t>[not stated]#ORG-074</t>
   </si>
   <si>
+    <t>fr-observation-naissance-document</t>
+  </si>
+  <si>
+    <t>Observation - Fr Naissance</t>
+  </si>
+  <si>
+    <t>null#118215003</t>
+  </si>
+  <si>
+    <t>fr-observation-recherche-micro-organismes</t>
+  </si>
+  <si>
+    <t>Observation - Fr Recherche de micro organismes</t>
+  </si>
+  <si>
+    <t>terminologie-cisis#MED-309</t>
+  </si>
+  <si>
     <t>fr-observation-renouvellement</t>
   </si>
   <si>
     <t>Observation - Fr renouvellement de l'acte</t>
   </si>
   <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#GEN-300</t>
+    <t>terminologie-cisis#GEN-300</t>
+  </si>
+  <si>
+    <t>fr-observation-statut</t>
+  </si>
+  <si>
+    <t>Observation - Fr Statut</t>
+  </si>
+  <si>
+    <t>null#106199-3</t>
+  </si>
+  <si>
+    <t>fr-observation-statut-document</t>
+  </si>
+  <si>
+    <t>Observation - Fr Statut du document</t>
+  </si>
+  <si>
+    <t>null#GEN-065</t>
+  </si>
+  <si>
+    <t>fr-observation-sur-echelle-douleur</t>
+  </si>
+  <si>
+    <t>Observation - Fr observation sur échelle de douleur</t>
+  </si>
+  <si>
+    <t>null#38208-5</t>
+  </si>
+  <si>
+    <t>integerĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-synthese-medicale-sejour-document</t>
+  </si>
+  <si>
+    <t>Observation - Fr Synthèse médicale du séjour</t>
+  </si>
+  <si>
+    <t>null#MED-142</t>
+  </si>
+  <si>
+    <t>fr-observation-transfusion-de-produits-sanguins</t>
+  </si>
+  <si>
+    <t>Observation - Fr Transfusion De Produits Sanguins</t>
+  </si>
+  <si>
+    <t>null#MED-145</t>
+  </si>
+  <si>
+    <t>fr-signes-vital-Observe-document</t>
+  </si>
+  <si>
+    <t>Observation - Fr Signe Vital Observé</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis (required)</t>
+  </si>
+  <si>
+    <t>fr-signes-vitaux-document</t>
+  </si>
+  <si>
+    <t>Observation - Fr Signes Vitaux</t>
+  </si>
+  <si>
+    <t>null#85353-1</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult (extensible)</t>
   </si>
 </sst>
 </file>
@@ -355,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -448,10 +553,10 @@
         <v>13</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>22</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>17</v>
@@ -465,25 +570,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="2">
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>26</v>
@@ -521,7 +626,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -556,7 +661,7 @@
         <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -591,7 +696,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -620,13 +725,13 @@
         <v>38</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -640,10 +745,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -652,7 +757,7 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>13</v>
@@ -661,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -675,10 +780,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -687,7 +792,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>13</v>
@@ -696,7 +801,7 @@
         <v>15</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>17</v>
@@ -710,10 +815,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>13</v>
@@ -722,16 +827,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -745,10 +850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>13</v>
@@ -757,7 +862,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>13</v>
@@ -766,7 +871,7 @@
         <v>15</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -780,28 +885,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>45</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>17</v>
@@ -815,13 +920,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -830,13 +935,13 @@
         <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -853,7 +958,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -871,7 +976,7 @@
         <v>13</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -885,13 +990,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>13</v>
@@ -900,13 +1005,13 @@
         <v>13</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -920,28 +1025,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>17</v>
@@ -955,10 +1060,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>13</v>
@@ -967,16 +1072,16 @@
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -990,10 +1095,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1002,24 +1107,374 @@
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K19" t="s" s="2">
+      <c r="H21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>13</v>
       </c>
     </row>
